--- a/business-libraries/test-data/class_system/output_template.xlsx
+++ b/business-libraries/test-data/class_system/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL-C-RED-SUMMARY</v>
+        <v>CLASS_SYSTEM_TPL_SURVIVAL_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>survival</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>评估显示，您在「${维度名1}」和「${维度名2}」两个维度上的得分同时处于高危水平。纪律与凝聚力双低，需要优先关注。</v>
+        <v>班级当前处于生存期，多个子系统同时薄弱，最突出的是「${主要归因}」。这个阶段的重点不是全面建设，而是先稳住秩序：选一个系统，做一件能立刻见效的事。</v>
       </c>
       <c r="F2" t="str">
-        <v>${维度名1} ${维度名2} 会被替换为实际触发红线的维度中文名</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL-C-RED-CONCLUSION</v>
+        <v>CLASS_SYSTEM_TPL_NORMING_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>red</v>
+        <v>norming</v>
       </c>
       <c r="D3" t="str">
-        <v>conclusion</v>
+        <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>本次评估结论：${主归因}（${次归因}）。已触发安全熔断，常规建议暂停输出。</v>
+        <v>班级处于规范期，当前最需要建设的是「${主要归因}」，同时「${次要归因}」也值得关注。这类问题通常不靠一次提醒解决，需要转化为可观察的班级机制。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主归因} 来自归因-分级规则.主归因；${次归因} 来自归因-分级规则.次归因</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL-C-RED-GOAL</v>
+        <v>CLASS_SYSTEM_TPL_OPERATING_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>red</v>
+        <v>operating</v>
       </c>
       <c r="D4" t="str">
-        <v>goal</v>
+        <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>当前首要目标：1) 确保教师获得即时心理支持 2) 降低当前的急性压力水平 3) 建立至少一个可依赖的支持关系</v>
+        <v>班级已经能够自主运行，可以聚焦「${主要归因}」做精细建设。相对稳定的部分可以作为带动全班调整的支点。</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,76 +493,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL-C-ORANGE-ATTRIBUTION</v>
+        <v>CLASS_SYSTEM_TPL_MATURE_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>orange</v>
+        <v>mature</v>
       </c>
       <c r="D5" t="str">
-        <v>attribution</v>
+        <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>本次评估的归因分析：${主归因}。建议重点关注以下方面：${工具标签}</v>
+        <v>班级系统运行成熟，建议把已有的做法沉淀成可交接的班级手册，让经验不随班主任变动而流失。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主归因} ${工具标签} 从归因规则中取值</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TPL-C-ORANGE-ACTION</v>
-      </c>
-      <c r="B6" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C6" t="str">
-        <v>orange</v>
-      </c>
-      <c r="D6" t="str">
-        <v>action</v>
-      </c>
-      <c r="E6" t="str">
-        <v>根据评估结果，建议采取以下行动：${输出动作摘要}。推荐工具：${输出工具摘要}。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>${输出动作摘要} ${输出工具摘要} 从归因规则中取值</v>
-      </c>
-      <c r="G6" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TPL-C-GREEN-SUMMARY</v>
-      </c>
-      <c r="B7" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C7" t="str">
-        <v>green</v>
-      </c>
-      <c r="D7" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E7" t="str">
-        <v>本次评估结果整体良好，各项指标均在正常范围内。继续保持现有节奏。</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/output_template.xlsx
+++ b/business-libraries/test-data/class_system/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CLASS_SYSTEM_TPL_SURVIVAL_SUMMARY</v>
+        <v>TPL_CS_RED_1</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>survival</v>
+        <v>red</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>班级当前处于生存期，多个子系统同时薄弱，最突出的是「${主要归因}」。这个阶段的重点不是全面建设，而是先稳住秩序：选一个系统，做一件能立刻见效的事。</v>
+        <v>班级整体信号已达到危机水平，常规建设手段已不足以应对。请立即联系年级组长与心理专员，暂停非必要的活动安排。</v>
       </c>
       <c r="F2" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CLASS_SYSTEM_TPL_NORMING_SUMMARY</v>
+        <v>TPL_CS_ORANGE_2</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>norming</v>
+        <v>orange</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>班级处于规范期，当前最需要建设的是「${主要归因}」，同时「${次要归因}」也值得关注。这类问题通常不靠一次提醒解决，需要转化为可观察的班级机制。</v>
+        <v>班级各系统信号整体偏弱，处于「秩序奠基」阶段。建议先稳住基本秩序，从推荐工具中选一项本周落地。</v>
       </c>
       <c r="F3" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CLASS_SYSTEM_TPL_OPERATING_SUMMARY</v>
+        <v>TPL_CS_YELLOW_3</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>operating</v>
+        <v>yellow</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>班级已经能够自主运行，可以聚焦「${主要归因}」做精细建设。相对稳定的部分可以作为带动全班调整的支点。</v>
+        <v>班级正在从「秩序奠基」走向「关系激活」，信号集中在「${主要归因}」。建议重点建设师生与同伴联结，两周后复评。</v>
       </c>
       <c r="F4" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,30 +493,53 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CLASS_SYSTEM_TPL_MATURE_SUMMARY</v>
+        <v>TPL_CS_BLUE_4</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>mature</v>
+        <v>blue</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>班级系统运行成熟，建议把已有的做法沉淀成可交接的班级手册，让经验不随班主任变动而流失。</v>
+        <v>班级已进入「制度自转」，事务分工与规则开始自主运转。建议把个别化做法沉淀为可复用机制，两周后复评。</v>
       </c>
       <c r="F5" t="str">
-        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
+        <v>可用占位符见 ⑩ 说明</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TPL_CS_DEFAULT</v>
+      </c>
+      <c r="B6" t="str">
+        <v>class_system</v>
+      </c>
+      <c r="C6" t="str">
+        <v>green</v>
+      </c>
+      <c r="D6" t="str">
+        <v>summary</v>
+      </c>
+      <c r="E6" t="str">
+        <v>班级已进入「文化引领」阶段，各系统自主运转，保持现有节奏、关注文化建设即可。</v>
+      </c>
+      <c r="F6" t="str">
+        <v>兜底模板：命中未覆盖等级时使用</v>
+      </c>
+      <c r="G6" t="str">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/output_template.xlsx
+++ b/business-libraries/test-data/class_system/output_template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +424,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TPL_CS_RED_1</v>
+        <v>CLASS_SYSTEM_TPL_SURVIVAL_SUMMARY</v>
       </c>
       <c r="B2" t="str">
         <v>class_system</v>
       </c>
       <c r="C2" t="str">
-        <v>red</v>
+        <v>survival</v>
       </c>
       <c r="D2" t="str">
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>班级整体信号已达到危机水平，常规建设手段已不足以应对。请立即联系年级组长与心理专员，暂停非必要的活动安排。</v>
+        <v>班级当前处于生存期，多个子系统同时薄弱，最突出的是「${主要归因}」。这个阶段的重点不是全面建设，而是先稳住秩序：选一个系统，做一件能立刻见效的事。</v>
       </c>
       <c r="F2" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G2" t="str">
         <v>1</v>
@@ -447,22 +447,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TPL_CS_ORANGE_2</v>
+        <v>CLASS_SYSTEM_TPL_NORMING_SUMMARY</v>
       </c>
       <c r="B3" t="str">
         <v>class_system</v>
       </c>
       <c r="C3" t="str">
-        <v>orange</v>
+        <v>norming</v>
       </c>
       <c r="D3" t="str">
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>班级各系统信号整体偏弱，处于「秩序奠基」阶段。建议先稳住基本秩序，从推荐工具中选一项本周落地。</v>
+        <v>班级处于规范期，当前最需要建设的是「${主要归因}」，同时「${次要归因}」也值得关注。这类问题通常不靠一次提醒解决，需要转化为可观察的班级机制。</v>
       </c>
       <c r="F3" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G3" t="str">
         <v>2</v>
@@ -470,22 +470,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TPL_CS_YELLOW_3</v>
+        <v>CLASS_SYSTEM_TPL_OPERATING_SUMMARY</v>
       </c>
       <c r="B4" t="str">
         <v>class_system</v>
       </c>
       <c r="C4" t="str">
-        <v>yellow</v>
+        <v>operating</v>
       </c>
       <c r="D4" t="str">
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>班级正在从「秩序奠基」走向「关系激活」，信号集中在「${主要归因}」。建议重点建设师生与同伴联结，两周后复评。</v>
+        <v>班级已经能够自主运行，可以聚焦「${主要归因}」做精细建设。相对稳定的部分可以作为带动全班调整的支点。</v>
       </c>
       <c r="F4" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G4" t="str">
         <v>3</v>
@@ -493,53 +493,30 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TPL_CS_BLUE_4</v>
+        <v>CLASS_SYSTEM_TPL_MATURE_SUMMARY</v>
       </c>
       <c r="B5" t="str">
         <v>class_system</v>
       </c>
       <c r="C5" t="str">
-        <v>blue</v>
+        <v>mature</v>
       </c>
       <c r="D5" t="str">
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>班级已进入「制度自转」，事务分工与规则开始自主运转。建议把个别化做法沉淀为可复用机制，两周后复评。</v>
+        <v>班级系统运行成熟，建议把已有的做法沉淀成可交接的班级手册，让经验不随班主任变动而流失。</v>
       </c>
       <c r="F5" t="str">
-        <v>可用占位符见 ⑩ 说明</v>
+        <v>${主要归因} 替换为占比最高的归因名称；${次要归因} 替换为第 2-3 条归因名称</v>
       </c>
       <c r="G5" t="str">
         <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TPL_CS_DEFAULT</v>
-      </c>
-      <c r="B6" t="str">
-        <v>class_system</v>
-      </c>
-      <c r="C6" t="str">
-        <v>green</v>
-      </c>
-      <c r="D6" t="str">
-        <v>summary</v>
-      </c>
-      <c r="E6" t="str">
-        <v>班级已进入「文化引领」阶段，各系统自主运转，保持现有节奏、关注文化建设即可。</v>
-      </c>
-      <c r="F6" t="str">
-        <v>兜底模板：命中未覆盖等级时使用</v>
-      </c>
-      <c r="G6" t="str">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/class_system/output_template.xlsx
+++ b/business-libraries/test-data/class_system/output_template.xlsx
@@ -436,7 +436,7 @@
         <v>summary</v>
       </c>
       <c r="E2" t="str">
-        <v>班级整体信号已达到危机水平，常规建设手段已不足以应对。请立即联系年级组长与心理专员，暂停非必要的活动安排。</v>
+        <v>A级（安全危机）或 B级（高风险）点检命中：该生存在自伤/伤他等安全风险。请立即停止常规建议输出，24-48小时内上报学校并通知心理专员，A级同时联系公安/医疗转介，全程留痕。</v>
       </c>
       <c r="F2" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -459,7 +459,7 @@
         <v>summary</v>
       </c>
       <c r="E3" t="str">
-        <v>班级各系统信号整体偏弱，处于「秩序奠基」阶段。建议先稳住基本秩序，从推荐工具中选一项本周落地。</v>
+        <v>五系统自评总分低于30分（或关系系统严重偏低）：班级处于系统性危机边缘，常规建设手段已不足以应对。请立即联系年级组长与心理专员，启动分层干预与学校支援。</v>
       </c>
       <c r="F3" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -482,7 +482,7 @@
         <v>summary</v>
       </c>
       <c r="E4" t="str">
-        <v>班级正在从「秩序奠基」走向「关系激活」，信号集中在「${主要归因}」。建议重点建设师生与同伴联结，两周后复评。</v>
+        <v>五系统自评总分30-59分：班级存在系统性问题或待建设弱项（${主要归因}），建议按短板启动重建或挑1-2个弱项做4周专项，从推荐工具中选一项本周落地，4周后复评。</v>
       </c>
       <c r="F4" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -505,7 +505,7 @@
         <v>summary</v>
       </c>
       <c r="E5" t="str">
-        <v>班级已进入「制度自转」，事务分工与规则开始自主运转。建议把个别化做法沉淀为可复用机制，两周后复评。</v>
+        <v>能量场问卷显示班级能量偏低（情感/关系维度尤为明显）：五系统自评总体健康但具体维度存在短板，建议结合五系统自评定位弱项，安排4周专项建设后复评。</v>
       </c>
       <c r="F5" t="str">
         <v>可用占位符见 ⑩ 说明</v>
@@ -528,7 +528,7 @@
         <v>summary</v>
       </c>
       <c r="E6" t="str">
-        <v>班级已进入「文化引领」阶段，各系统自主运转，保持现有节奏、关注文化建设即可。</v>
+        <v>五系统自评总分60-75分：班级健康，各系统自主运转，已进入文化生成期，保持现有节奏、持续沉淀班级文化即可。</v>
       </c>
       <c r="F6" t="str">
         <v>兜底模板：命中未覆盖等级时使用</v>
